--- a/public/modelo-importacao.xlsx
+++ b/public/modelo-importacao.xlsx
@@ -1,50 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet sheetId="1" name="Funcionários" state="visible" r:id="rId4"/>
+    <sheet name="Funcionários" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t>Nome</t>
-  </si>
-  <si>
-    <t>CPF</t>
-  </si>
-  <si>
-    <t>Telefone</t>
-  </si>
-  <si>
-    <t>Chave Pix</t>
-  </si>
-  <si>
-    <t>Empresa/Setor</t>
-  </si>
-  <si>
-    <t>Cargo</t>
-  </si>
-  <si>
-    <t>Valor</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
+      <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -68,21 +65,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -407,40 +396,100 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H3"/>
   <cols>
-    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" customWidth="1"/>
+    <col min="7" max="7" width="24.83203125" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Nome</v>
+      </c>
+      <c r="B1" t="str">
+        <v>CPF</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Telefone</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Empresa/Setor</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Cargo</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Cidade</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Chave Pix</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Valor</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25"/>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Ana Beatriz Ramos</v>
+      </c>
+      <c r="B2" t="str">
+        <v>123.456.789-09</v>
+      </c>
+      <c r="C2" t="str">
+        <v>(27) 99999-9999</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Bar</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Barman</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Vitória</v>
+      </c>
+      <c r="G2" t="str">
+        <v>ana@email.com</v>
+      </c>
+      <c r="H2" t="str">
+        <v>150,00</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v/>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/public/modelo-importacao.xlsx
+++ b/public/modelo-importacao.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Funcionários" sheetId="1" r:id="rId1"/>
+    <sheet name="Equipe" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,16 +397,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:G2"/>
   <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
     <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="24.83203125" customWidth="1"/>
-    <col min="8" max="8" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="22.83203125" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -420,24 +419,21 @@
         <v>Telefone</v>
       </c>
       <c r="D1" t="str">
-        <v>Empresa/Setor</v>
+        <v>Cargo</v>
       </c>
       <c r="E1" t="str">
-        <v>Cargo</v>
+        <v>Cidade</v>
       </c>
       <c r="F1" t="str">
-        <v>Cidade</v>
+        <v>Chave Pix</v>
       </c>
       <c r="G1" t="str">
-        <v>Chave Pix</v>
-      </c>
-      <c r="H1" t="str">
         <v>Valor</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Ana Beatriz Ramos</v>
+        <v>APAGUE ESTA LINHA — exemplo</v>
       </c>
       <c r="B2" t="str">
         <v>123.456.789-09</v>
@@ -446,50 +442,21 @@
         <v>(27) 99999-9999</v>
       </c>
       <c r="D2" t="str">
-        <v>Bar</v>
+        <v>Barman</v>
       </c>
       <c r="E2" t="str">
-        <v>Barman</v>
+        <v>Vitória</v>
       </c>
       <c r="F2" t="str">
-        <v>Vitória</v>
+        <v>chave@email.com</v>
       </c>
       <c r="G2" t="str">
-        <v>ana@email.com</v>
-      </c>
-      <c r="H2" t="str">
         <v>150,00</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v/>
-      </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
   </ignoredErrors>
 </worksheet>
 </file>